--- a/codespace/promodel_inputs/ProModel_tables.xlsx
+++ b/codespace/promodel_inputs/ProModel_tables.xlsx
@@ -4116,14 +4116,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4252,58 +4252,88 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mSiteLimitkW</t>
+          <t>mPBalk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20 - 150</t>
+          <t>0.5 - 1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>kW</t>
+          <t>probability</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>site power cap (stage 5)</t>
+          <t>leave at once when all EVSEs are busy (stage 5)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lee et al. 2021a; acnportal (150 kVA transformer)</t>
+          <t>assumption (R02)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>mSiteLimitkW</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20 - 150</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>site power cap (stage 5)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lee et al. 2021a; acnportal (150 kVA transformer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>mPolicy</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1 uncontrolled / 2 equal share / 3 earliest departure first / 4 move after charge</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>charging policy (stage 5)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>proposal</t>
         </is>

--- a/codespace/promodel_inputs/ProModel_tables.xlsx
+++ b/codespace/promodel_inputs/ProModel_tables.xlsx
@@ -15,8 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Energy" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empirical tables" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User class" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macros" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announced inputs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unclaimed by dwell" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Macros" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Announced inputs" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,35 +522,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>User distribution dUserClass (discrete)</t>
+          <t>User distribution dUserClass (discrete): overall shares, for reference and stage 4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Macros</t>
+          <t>Unclaimed by dwell</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scenario macros with baseline and test values</t>
+          <t>Share of unclaimed sessions by dwell bin: aUserClass is drawn after aDwell from these</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Macros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Scenario macros with baseline and test values</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Announced inputs</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Announced-input error quantiles (for aDepAnnounced and aEnergyReq in later stages)</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -725,6 +737,240 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Scenario values</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Used in</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mPorts</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>30 / 42 / 54 / 66</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>EVSEs</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EVSE_BANK capacity</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garage 01 has 54 Level-2 EVSEs; proposal factor levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mRate</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.17 / 4.8 / 6.66</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>constant effective charging rate (stages 1-3)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>median observed kWh per charging hour (n=16140); 4.8 = vehicle-rate mix mean; 6.66 = EVSE rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mDemand</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.8 / 1.0 / 1.2 / 1.5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>x daily arrivals</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Arrivals Qty Each</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>proposal (R17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mPBalk</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.5 - 1.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>probability</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>leave at once when all EVSEs are busy (stage 5)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>assumption (R02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mSiteLimitkW</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>20 - 150</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>site power cap (stage 5)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lee et al. 2021a; acnportal (150 kVA transformer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mPolicy</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1 uncontrolled / 2 equal share / 3 earliest departure first / 4 move after charge</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>charging policy (stage 5)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>proposal</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4116,227 +4362,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Dwell (h)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Scenario values</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Used in</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>Unclaimed share %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mPorts</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>30 / 42 / 54 / 66</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EVSEs</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EVSE_BANK capacity</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garage 01 has 54 Level-2 EVSEs; proposal factor levels</t>
-        </is>
+        <v>27.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mRate</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.17 / 4.8 / 6.66</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>kW</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>constant effective charging rate (stages 1-3)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>median observed kWh per charging hour (n=16140); 4.8 = vehicle-rate mix mean; 6.66 = EVSE rating</t>
-        </is>
+        <v>18.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mDemand</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.8 / 1.0 / 1.2 / 1.5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>x daily arrivals</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Arrivals Qty Each</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>proposal (R17)</t>
-        </is>
+        <v>13.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mPBalk</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.5 - 1.0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>probability</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>leave at once when all EVSEs are busy (stage 5)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>assumption (R02)</t>
-        </is>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mSiteLimitkW</t>
+          <t>8-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>150</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>20 - 150</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>kW</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>site power cap (stage 5)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lee et al. 2021a; acnportal (150 kVA transformer)</t>
-        </is>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mPolicy</t>
+          <t>10-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1 uncontrolled / 2 equal share / 3 earliest departure first / 4 move after charge</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>charging policy (stage 5)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>proposal</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/codespace/promodel_inputs/ProModel_tables.xlsx
+++ b/codespace/promodel_inputs/ProModel_tables.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Continuous cumulative user distributions for the groups whose best fit has KS &gt; 0.1</t>
+          <t>Continuous cumulative user distributions for the groups whose best fit has KS &gt; 0.1 (P0-P90 by 10, P95, P99, P100)</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3676,46 +3676,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>22.47</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dDwellWD0709</t>
+          <t>dDwellWD0007</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>weekday 07-09</t>
+          <t>weekday 00-07</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>0.11</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dDwellWD0709</t>
+          <t>dDwellWD0007</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>weekday 07-09</t>
+          <t>weekday 00-07</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>2.79</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="15">
@@ -3730,10 +3730,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4.21</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="16">
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>6.13</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="17">
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>7.67</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="18">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>8.42</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="19">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
-        <v>8.789999999999999</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="20">
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>9.109999999999999</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="21">
@@ -3838,10 +3838,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>9.59</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D22" t="n">
-        <v>10.27</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3874,82 +3874,82 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D23" t="n">
-        <v>22.32</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dDwellWD0911</t>
+          <t>dDwellWD0709</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>weekday 09-11</t>
+          <t>weekday 07-09</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>0.09</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dDwellWD0911</t>
+          <t>dDwellWD0709</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>weekday 09-11</t>
+          <t>weekday 07-09</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="D25" t="n">
-        <v>1.98</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dDwellWD0911</t>
+          <t>dDwellWD0709</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>weekday 09-11</t>
+          <t>weekday 07-09</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D26" t="n">
-        <v>3.9</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dDwellWD0911</t>
+          <t>dDwellWD0709</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>weekday 09-11</t>
+          <t>weekday 07-09</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D27" t="n">
-        <v>6.11</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="28">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>6.98</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="29">
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>7.5</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="30">
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D30" t="n">
-        <v>7.95</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="31">
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>8.43</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="32">
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D32" t="n">
-        <v>8.960000000000001</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="33">
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D33" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34">
@@ -4072,118 +4072,118 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D34" t="n">
-        <v>23.92</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5</v>
+        <v>8.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D36" t="n">
-        <v>0.77</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D37" t="n">
-        <v>0.83</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="D38" t="n">
-        <v>0.85</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="D39" t="n">
-        <v>0.87</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dEnergyUnclaimed</t>
+          <t>dDwellWD0911</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>unclaimed (30-min auto stop)</t>
+          <t>weekday 09-11</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D40" t="n">
-        <v>0.89</v>
+        <v>23.92</v>
       </c>
     </row>
     <row r="41">
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="43">
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D43" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="44">
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D44" t="n">
-        <v>1.19</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="45">
@@ -4270,9 +4270,153 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>40</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>50</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>60</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>80</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>90</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>95</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>99</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4.92</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>dEnergyUnclaimed</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>unclaimed (30-min auto stop)</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
         <v>100</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D53" t="n">
         <v>11.81</v>
       </c>
     </row>

--- a/codespace/promodel_inputs/ProModel_tables.xlsx
+++ b/codespace/promodel_inputs/ProModel_tables.xlsx
@@ -749,7 +749,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -836,7 +836,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>constant effective charging rate (stages 1-3)</t>
+          <t>normal charging rate; at service start code B raises a car's rate to aEnergyNeed / remaining time when needed, up to 6.66 kW</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/codespace/promodel_inputs/ProModel_tables.xlsx
+++ b/codespace/promodel_inputs/ProModel_tables.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>normal charging rate; at service start code B raises a car's rate to aEnergyNeed / remaining time when needed, up to 6.66 kW</t>
+          <t>normal charging rate: at service start code B sets aRate = aEnergyNeed / remaining time, at least mRate and at most aMaxRate (6.66 kW in stages 1-3)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
